--- a/Team-Data/2012-13/2-28-2012-13.xlsx
+++ b/Team-Data/2012-13/2-28-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -757,7 +824,7 @@
         <v>11</v>
       </c>
       <c r="AJ2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK2" t="n">
         <v>7</v>
@@ -799,7 +866,7 @@
         <v>15</v>
       </c>
       <c r="AX2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY2" t="n">
         <v>7</v>
@@ -814,7 +881,7 @@
         <v>14</v>
       </c>
       <c r="BC2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-28-2012-13</t>
+          <t>2013-02-28</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>0.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE3" t="n">
         <v>15</v>
@@ -984,7 +1051,7 @@
         <v>26</v>
       </c>
       <c r="AY3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ3" t="n">
         <v>27</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-28-2012-13</t>
+          <t>2013-02-28</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>0.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE4" t="n">
         <v>8</v>
@@ -1133,7 +1200,7 @@
         <v>7</v>
       </c>
       <c r="AN4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO4" t="n">
         <v>10</v>
@@ -1160,13 +1227,13 @@
         <v>11</v>
       </c>
       <c r="AW4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX4" t="n">
         <v>18</v>
       </c>
       <c r="AY4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ4" t="n">
         <v>2</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-28-2012-13</t>
+          <t>2013-02-28</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-9.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE5" t="n">
         <v>30</v>
@@ -1321,7 +1388,7 @@
         <v>2</v>
       </c>
       <c r="AP5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ5" t="n">
         <v>18</v>
@@ -1342,7 +1409,7 @@
         <v>6</v>
       </c>
       <c r="AW5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX5" t="n">
         <v>6</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-28-2012-13</t>
+          <t>2013-02-28</t>
         </is>
       </c>
     </row>
@@ -1389,28 +1456,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E6" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F6" t="n">
         <v>25</v>
       </c>
       <c r="G6" t="n">
-        <v>0.569</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I6" t="n">
-        <v>35.4</v>
+        <v>35.5</v>
       </c>
       <c r="J6" t="n">
         <v>81.2</v>
       </c>
       <c r="K6" t="n">
-        <v>0.436</v>
+        <v>0.437</v>
       </c>
       <c r="L6" t="n">
         <v>4.8</v>
@@ -1419,13 +1486,13 @@
         <v>14</v>
       </c>
       <c r="N6" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="O6" t="n">
-        <v>17</v>
+        <v>16.8</v>
       </c>
       <c r="P6" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="Q6" t="n">
         <v>0.779</v>
@@ -1434,55 +1501,55 @@
         <v>12.8</v>
       </c>
       <c r="S6" t="n">
-        <v>30.9</v>
+        <v>30.8</v>
       </c>
       <c r="T6" t="n">
-        <v>43.7</v>
+        <v>43.5</v>
       </c>
       <c r="U6" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="V6" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W6" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X6" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AB6" t="n">
         <v>92.59999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AF6" t="n">
         <v>11</v>
       </c>
       <c r="AG6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH6" t="n">
         <v>20</v>
       </c>
       <c r="AI6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ6" t="n">
         <v>20</v>
@@ -1503,16 +1570,16 @@
         <v>16</v>
       </c>
       <c r="AP6" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AQ6" t="n">
         <v>9</v>
       </c>
       <c r="AR6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AT6" t="n">
         <v>6</v>
@@ -1527,13 +1594,13 @@
         <v>20</v>
       </c>
       <c r="AX6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AY6" t="n">
         <v>22</v>
       </c>
       <c r="AZ6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA6" t="n">
         <v>14</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-28-2012-13</t>
+          <t>2013-02-28</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-3.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE7" t="n">
         <v>23</v>
@@ -1679,7 +1746,7 @@
         <v>11</v>
       </c>
       <c r="AN7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO7" t="n">
         <v>11</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-28-2012-13</t>
+          <t>2013-02-28</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>-1.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE8" t="n">
         <v>19</v>
@@ -1867,7 +1934,7 @@
         <v>12</v>
       </c>
       <c r="AP8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ8" t="n">
         <v>3</v>
@@ -1891,7 +1958,7 @@
         <v>16</v>
       </c>
       <c r="AX8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY8" t="n">
         <v>5</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-28-2012-13</t>
+          <t>2013-02-28</t>
         </is>
       </c>
     </row>
@@ -2013,16 +2080,16 @@
         <v>3.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE9" t="n">
         <v>6</v>
       </c>
       <c r="AF9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH9" t="n">
         <v>8</v>
@@ -2052,7 +2119,7 @@
         <v>3</v>
       </c>
       <c r="AQ9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AR9" t="n">
         <v>1</v>
@@ -2067,7 +2134,7 @@
         <v>3</v>
       </c>
       <c r="AV9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW9" t="n">
         <v>2</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-28-2012-13</t>
+          <t>2013-02-28</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2286,7 @@
         <v>15</v>
       </c>
       <c r="AL10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM10" t="n">
         <v>26</v>
@@ -2240,22 +2307,22 @@
         <v>9</v>
       </c>
       <c r="AS10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU10" t="n">
         <v>24</v>
       </c>
       <c r="AV10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW10" t="n">
         <v>27</v>
       </c>
       <c r="AX10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY10" t="n">
         <v>19</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-28-2012-13</t>
+          <t>2013-02-28</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>-0.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE11" t="n">
         <v>10</v>
@@ -2413,7 +2480,7 @@
         <v>14</v>
       </c>
       <c r="AP11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ11" t="n">
         <v>2</v>
@@ -2431,7 +2498,7 @@
         <v>11</v>
       </c>
       <c r="AV11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW11" t="n">
         <v>28</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-28-2012-13</t>
+          <t>2013-02-28</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>2.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
         <v>13</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-28-2012-13</t>
+          <t>2013-02-28</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E13" t="n">
         <v>36</v>
       </c>
       <c r="F13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G13" t="n">
-        <v>0.621</v>
+        <v>0.632</v>
       </c>
       <c r="H13" t="n">
         <v>48.5</v>
@@ -2681,7 +2748,7 @@
         <v>35.1</v>
       </c>
       <c r="J13" t="n">
-        <v>80.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="K13" t="n">
         <v>0.434</v>
@@ -2690,7 +2757,7 @@
         <v>6.9</v>
       </c>
       <c r="M13" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="N13" t="n">
         <v>0.354</v>
@@ -2705,13 +2772,13 @@
         <v>0.741</v>
       </c>
       <c r="R13" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="S13" t="n">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="T13" t="n">
-        <v>45.8</v>
+        <v>45.9</v>
       </c>
       <c r="U13" t="n">
         <v>20.5</v>
@@ -2735,13 +2802,13 @@
         <v>21.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>93.90000000000001</v>
+        <v>94</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AE13" t="n">
         <v>7</v>
@@ -2750,7 +2817,7 @@
         <v>7</v>
       </c>
       <c r="AG13" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AH13" t="n">
         <v>11</v>
@@ -2759,25 +2826,25 @@
         <v>28</v>
       </c>
       <c r="AJ13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK13" t="n">
         <v>27</v>
       </c>
       <c r="AL13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AM13" t="n">
         <v>15</v>
       </c>
-      <c r="AM13" t="n">
-        <v>14</v>
-      </c>
       <c r="AN13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO13" t="n">
         <v>17</v>
       </c>
       <c r="AP13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ13" t="n">
         <v>20</v>
@@ -2786,7 +2853,7 @@
         <v>4</v>
       </c>
       <c r="AS13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AT13" t="n">
         <v>1</v>
@@ -2795,10 +2862,10 @@
         <v>26</v>
       </c>
       <c r="AV13" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AW13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX13" t="n">
         <v>3</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-28-2012-13</t>
+          <t>2013-02-28</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E14" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F14" t="n">
         <v>18</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7</v>
+        <v>0.695</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
@@ -2866,16 +2933,16 @@
         <v>80.5</v>
       </c>
       <c r="K14" t="n">
-        <v>0.475</v>
+        <v>0.474</v>
       </c>
       <c r="L14" t="n">
         <v>7.3</v>
       </c>
       <c r="M14" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="N14" t="n">
-        <v>0.357</v>
+        <v>0.361</v>
       </c>
       <c r="O14" t="n">
         <v>16.7</v>
@@ -2884,22 +2951,22 @@
         <v>23.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.705</v>
+        <v>0.703</v>
       </c>
       <c r="R14" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S14" t="n">
         <v>30.3</v>
       </c>
       <c r="T14" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="U14" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="V14" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W14" t="n">
         <v>9.9</v>
@@ -2911,7 +2978,7 @@
         <v>4.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AA14" t="n">
         <v>21.1</v>
@@ -2923,10 +2990,10 @@
         <v>6.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF14" t="n">
         <v>4</v>
@@ -2953,7 +3020,7 @@
         <v>10</v>
       </c>
       <c r="AN14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AO14" t="n">
         <v>18</v>
@@ -2965,16 +3032,16 @@
         <v>27</v>
       </c>
       <c r="AR14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT14" t="n">
         <v>17</v>
       </c>
       <c r="AU14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV14" t="n">
         <v>20</v>
@@ -2989,7 +3056,7 @@
         <v>6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA14" t="n">
         <v>7</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-28-2012-13</t>
+          <t>2013-02-28</t>
         </is>
       </c>
     </row>
@@ -3027,46 +3094,46 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F15" t="n">
         <v>30</v>
       </c>
       <c r="G15" t="n">
-        <v>0.492</v>
+        <v>0.483</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
       </c>
       <c r="I15" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J15" t="n">
         <v>81.2</v>
       </c>
       <c r="K15" t="n">
-        <v>0.461</v>
+        <v>0.46</v>
       </c>
       <c r="L15" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="M15" t="n">
-        <v>24.2</v>
+        <v>24</v>
       </c>
       <c r="N15" t="n">
-        <v>0.358</v>
+        <v>0.355</v>
       </c>
       <c r="O15" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="P15" t="n">
-        <v>27.4</v>
+        <v>27.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R15" t="n">
         <v>11.6</v>
@@ -3075,10 +3142,10 @@
         <v>33.1</v>
       </c>
       <c r="T15" t="n">
-        <v>44.7</v>
+        <v>44.6</v>
       </c>
       <c r="U15" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="V15" t="n">
         <v>15.3</v>
@@ -3090,22 +3157,22 @@
         <v>5.3</v>
       </c>
       <c r="Y15" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Z15" t="n">
         <v>18.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="AB15" t="n">
-        <v>102.4</v>
+        <v>102.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AE15" t="n">
         <v>16</v>
@@ -3135,28 +3202,28 @@
         <v>3</v>
       </c>
       <c r="AN15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP15" t="n">
         <v>1</v>
       </c>
       <c r="AQ15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AR15" t="n">
         <v>12</v>
       </c>
       <c r="AS15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AT15" t="n">
         <v>4</v>
       </c>
       <c r="AU15" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AV15" t="n">
         <v>27</v>
@@ -3180,7 +3247,7 @@
         <v>6</v>
       </c>
       <c r="BC15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-28-2012-13</t>
+          <t>2013-02-28</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-28-2012-13</t>
+          <t>2013-02-28</t>
         </is>
       </c>
     </row>
@@ -3469,10 +3536,10 @@
         <v>7.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF17" t="n">
         <v>1</v>
@@ -3505,7 +3572,7 @@
         <v>13</v>
       </c>
       <c r="AP17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ17" t="n">
         <v>15</v>
@@ -3535,7 +3602,7 @@
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA17" t="n">
         <v>13</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-28-2012-13</t>
+          <t>2013-02-28</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3721,7 @@
         <v>23</v>
       </c>
       <c r="AE18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF18" t="n">
         <v>15</v>
@@ -3663,7 +3730,7 @@
         <v>16</v>
       </c>
       <c r="AH18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI18" t="n">
         <v>9</v>
@@ -3687,7 +3754,7 @@
         <v>24</v>
       </c>
       <c r="AP18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ18" t="n">
         <v>24</v>
@@ -3696,7 +3763,7 @@
         <v>3</v>
       </c>
       <c r="AS18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT18" t="n">
         <v>5</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-28-2012-13</t>
+          <t>2013-02-28</t>
         </is>
       </c>
     </row>
@@ -3755,22 +3822,22 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E19" t="n">
         <v>20</v>
       </c>
       <c r="F19" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G19" t="n">
-        <v>0.364</v>
+        <v>0.37</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
       </c>
       <c r="I19" t="n">
-        <v>35.5</v>
+        <v>35.4</v>
       </c>
       <c r="J19" t="n">
         <v>81.5</v>
@@ -3782,34 +3849,34 @@
         <v>5.4</v>
       </c>
       <c r="M19" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="N19" t="n">
         <v>0.3</v>
       </c>
       <c r="O19" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="P19" t="n">
-        <v>25.7</v>
+        <v>25.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.735</v>
+        <v>0.733</v>
       </c>
       <c r="R19" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="S19" t="n">
         <v>30.5</v>
       </c>
       <c r="T19" t="n">
-        <v>43.2</v>
+        <v>43.4</v>
       </c>
       <c r="U19" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="V19" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W19" t="n">
         <v>8.199999999999999</v>
@@ -3824,16 +3891,16 @@
         <v>18.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AB19" t="n">
         <v>95.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>-2.5</v>
+        <v>-2.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE19" t="n">
         <v>23</v>
@@ -3848,7 +3915,7 @@
         <v>26</v>
       </c>
       <c r="AI19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ19" t="n">
         <v>18</v>
@@ -3866,28 +3933,28 @@
         <v>30</v>
       </c>
       <c r="AO19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ19" t="n">
         <v>23</v>
       </c>
       <c r="AR19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS19" t="n">
         <v>17</v>
       </c>
       <c r="AT19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AU19" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AV19" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AW19" t="n">
         <v>12</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-28-2012-13</t>
+          <t>2013-02-28</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-3.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE20" t="n">
         <v>23</v>
@@ -4075,7 +4142,7 @@
         <v>29</v>
       </c>
       <c r="AX20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY20" t="n">
         <v>25</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-28-2012-13</t>
+          <t>2013-02-28</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>3.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE21" t="n">
         <v>8</v>
@@ -4206,7 +4273,7 @@
         <v>6</v>
       </c>
       <c r="AG21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH21" t="n">
         <v>28</v>
@@ -4233,7 +4300,7 @@
         <v>19</v>
       </c>
       <c r="AP21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ21" t="n">
         <v>16</v>
@@ -4245,7 +4312,7 @@
         <v>22</v>
       </c>
       <c r="AT21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-28-2012-13</t>
+          <t>2013-02-28</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4406,7 +4473,7 @@
         <v>10</v>
       </c>
       <c r="AM22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AN22" t="n">
         <v>2</v>
@@ -4430,7 +4497,7 @@
         <v>10</v>
       </c>
       <c r="AU22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV22" t="n">
         <v>29</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-28-2012-13</t>
+          <t>2013-02-28</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-5.9</v>
       </c>
       <c r="AD23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE23" t="n">
         <v>29</v>
@@ -4612,7 +4679,7 @@
         <v>13</v>
       </c>
       <c r="AU23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV23" t="n">
         <v>12</v>
@@ -4630,7 +4697,7 @@
         <v>8</v>
       </c>
       <c r="BA23" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB23" t="n">
         <v>24</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-28-2012-13</t>
+          <t>2013-02-28</t>
         </is>
       </c>
     </row>
@@ -4665,34 +4732,34 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E24" t="n">
         <v>22</v>
       </c>
       <c r="F24" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G24" t="n">
-        <v>0.393</v>
+        <v>0.4</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
       </c>
       <c r="I24" t="n">
-        <v>36.8</v>
+        <v>36.9</v>
       </c>
       <c r="J24" t="n">
-        <v>83.8</v>
+        <v>83.7</v>
       </c>
       <c r="K24" t="n">
-        <v>0.44</v>
+        <v>0.441</v>
       </c>
       <c r="L24" t="n">
         <v>6.1</v>
       </c>
       <c r="M24" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="N24" t="n">
         <v>0.35</v>
@@ -4701,49 +4768,49 @@
         <v>12.1</v>
       </c>
       <c r="P24" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.72</v>
+        <v>0.723</v>
       </c>
       <c r="R24" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S24" t="n">
-        <v>30.6</v>
+        <v>30.5</v>
       </c>
       <c r="T24" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="U24" t="n">
-        <v>22.1</v>
+        <v>22.3</v>
       </c>
       <c r="V24" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="W24" t="n">
         <v>7.1</v>
       </c>
       <c r="X24" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>91.8</v>
+        <v>92</v>
       </c>
       <c r="AC24" t="n">
-        <v>-3.9</v>
+        <v>-3.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AE24" t="n">
         <v>22</v>
@@ -4752,7 +4819,7 @@
         <v>20</v>
       </c>
       <c r="AG24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH24" t="n">
         <v>22</v>
@@ -4767,7 +4834,7 @@
         <v>22</v>
       </c>
       <c r="AL24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM24" t="n">
         <v>23</v>
@@ -4785,34 +4852,34 @@
         <v>25</v>
       </c>
       <c r="AR24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS24" t="n">
         <v>16</v>
       </c>
       <c r="AT24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV24" t="n">
         <v>2</v>
       </c>
       <c r="AW24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY24" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ24" t="n">
         <v>7</v>
       </c>
       <c r="BA24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-28-2012-13</t>
+          <t>2013-02-28</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>-5.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="n">
         <v>23</v>
@@ -4967,7 +5034,7 @@
         <v>19</v>
       </c>
       <c r="AR25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS25" t="n">
         <v>21</v>
@@ -4985,13 +5052,13 @@
         <v>17</v>
       </c>
       <c r="AX25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY25" t="n">
         <v>17</v>
       </c>
       <c r="AZ25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA25" t="n">
         <v>28</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-28-2012-13</t>
+          <t>2013-02-28</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-2.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE26" t="n">
         <v>18</v>
@@ -5152,7 +5219,7 @@
         <v>18</v>
       </c>
       <c r="AS26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT26" t="n">
         <v>19</v>
@@ -5161,7 +5228,7 @@
         <v>22</v>
       </c>
       <c r="AV26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW26" t="n">
         <v>26</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-28-2012-13</t>
+          <t>2013-02-28</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-6.7</v>
       </c>
       <c r="AD27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE27" t="n">
         <v>23</v>
@@ -5313,7 +5380,7 @@
         <v>20</v>
       </c>
       <c r="AL27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM27" t="n">
         <v>18</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-28-2012-13</t>
+          <t>2013-02-28</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5507,7 +5574,7 @@
         <v>15</v>
       </c>
       <c r="AP28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ28" t="n">
         <v>4</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-28-2012-13</t>
+          <t>2013-02-28</t>
         </is>
       </c>
     </row>
@@ -5653,16 +5720,16 @@
         <v>-1.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE29" t="n">
         <v>20</v>
       </c>
       <c r="AF29" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG29" t="n">
         <v>21</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>20</v>
       </c>
       <c r="AH29" t="n">
         <v>3</v>
@@ -5704,7 +5771,7 @@
         <v>28</v>
       </c>
       <c r="AU29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV29" t="n">
         <v>3</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-28-2012-13</t>
+          <t>2013-02-28</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-0.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE30" t="n">
         <v>13</v>
@@ -5847,7 +5914,7 @@
         <v>13</v>
       </c>
       <c r="AH30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI30" t="n">
         <v>15</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-28-2012-13</t>
+          <t>2013-02-28</t>
         </is>
       </c>
     </row>
@@ -6047,7 +6114,7 @@
         <v>19</v>
       </c>
       <c r="AN31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO31" t="n">
         <v>27</v>
@@ -6059,16 +6126,16 @@
         <v>21</v>
       </c>
       <c r="AR31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS31" t="n">
         <v>7</v>
       </c>
       <c r="AT31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV31" t="n">
         <v>28</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-28-2012-13</t>
+          <t>2013-02-28</t>
         </is>
       </c>
     </row>
